--- a/02_加值成品/八上/八上1-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-4_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上1-4 密度　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上1-4 密度　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>密度的公式是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>下沉</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>D=M/V</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>可初步判別</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>質量除體積</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>水的密度約為多少？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>1 g/cm³</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>2.7 g/cm³</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>g/cm³、kg/m³</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>平均密度(含空間)小於水</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>常用值</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>密度常用單位有哪些？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>g/cm³、kg/m³</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>2.7 g/cm³</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>測密度是否為19.3</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2 g/cm³</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>兩種</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>密度是物質的什麼？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>特性</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>排水法</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>上浮</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>可辨別物質</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>物體密度大於水會怎樣？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>排水法</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>下沉</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>上浮</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>密度較大</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>物體密度小於水會怎樣？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>下沉</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>上浮</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>特性</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>密度較小</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>量質量用什麼工具？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>天平</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>排水法</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>稱質量</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>量不規則物體積用？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>下沉</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>排水法</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>小於水</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>排開水體積</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>密度相同能否初步判別為同物質？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>D=M/V</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>小於水</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>可初步判別</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>減半</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>特性</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>冰的密度比水大還小？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>下沉</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>天平</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>鐵,密度較大</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>小</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>浮於水</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上1-4 密度　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上1-4 密度　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>質量40g、體積5cm³，密度？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>8 g/cm³</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>測密度是否為19.3</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2 g/cm³</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>2.7 g/cm³</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>40/5</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>密度2g/cm³、體積10cm³，質量？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>20 g</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>減半</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>1 g/cm³</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>D×V</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>一物切成一半，密度變？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>天平</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>特性</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>上浮</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>特性不變</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>密度0.8g/cm³的油放入水中？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>上浮</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>水銀</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>減半</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>小於水</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>質量54g的鋁塊體積20cm³，密度？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>測密度是否為19.3</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>1 g/cm³</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>2.7 g/cm³</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>8 g/cm³</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>鋁密度</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>密度13.6g/cm³最可能是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>水銀</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>上浮</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>排水法</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>特性</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>高密度液</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>體積2cm³、質量16g，密度？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>g/cm³、kg/m³</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>測密度是否為19.3</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>8 g/cm³</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>浮,密度0.8&lt;1</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>16/2</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>1 g/cm³ 等於幾 kg/m³？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>水銀</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>特性</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3 g/cm³</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>單位換算</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>質量100g體積50cm³密度？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>平均密度(含空間)小於水</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>測密度是否為19.3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>2 g/cm³</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1 g/cm³</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>100/50</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>密度4g/cm³體積3cm³質量？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>12 g</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>1 g/cm³</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>D×V</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上1-4 密度　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上1-4 密度　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>鐵球與鐵屑密度相同嗎？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>D=M/V</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>相同</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>可初步判別</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>下沉</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>同物質特性</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>大船是鐵做的為何能浮？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>g/cm³、kg/m³</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>平均密度(含空間)小於水</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>3 g/cm³</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>2 g/cm³</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>整體考量</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>冰浮在水上代表冰密度？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>下層</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>下沉</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>小於水</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>減半</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>約0.92</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>兩液體不互溶，密度大的在？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>天平</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>鐵,密度較大</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>下層</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>分層</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>質量M體積V密度D，V加倍M不變則D？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>上浮</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>可初步判別</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>D=M/V</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>減半</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>反比</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>60g物體在水中排開20cm³水，密度？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>g/cm³、kg/m³</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>1 g/cm³</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>2.7 g/cm³</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>3 g/cm³</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>60/20</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>如何用密度分辨純金與鍍金？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>平均密度(含空間)小於水</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>2.7 g/cm³</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>g/cm³、kg/m³</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>測密度是否為19.3</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>比對特性值</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>氣體密度比固體液體如何？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>下沉</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>特性</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>小很多</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>上浮</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>分子間距大</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>同體積的鐵與鋁誰較重?為何</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>鐵,密度較大</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>下沉</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>小很多</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>上浮</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>密度</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>20g物體排開25cm³水會浮或沉?為何</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>g/cm³、kg/m³</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>浮,密度0.8&lt;1</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>3 g/cm³</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>2.7 g/cm³</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>浮沉</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上1-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-4_三種難度測驗卷.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>單位換算</t>
+          <t>1g=10⁻³kg,1cm³=10⁻⁶m³,相除×1000</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上1-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-4_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>質量除體積</t>
+          <t>質量除體積：密度的定義是質量除以體積，公式寫作D=M/V</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>常用值</t>
+          <t>常用值：常溫下水的密度約為1克每立方公分，是判斷物體能否浮於水面的常用比較值</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>兩種</t>
+          <t>兩種：密度最常用的單位是g/cm³(克每立方公分)和kg/m³(公斤每立方公尺)</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>可辨別物質</t>
+          <t>可辨別物質：密度是每種物質固有的特性，同一物質不論形狀大小密度都相同，可用來幫助辨別物質種類</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>密度較大</t>
+          <t>密度較大：物體密度比水大，代表相同體積下它比水重，會下沉</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>密度較小</t>
+          <t>密度較小：物體密度比水小，代表相同體積下它比水輕，會浮在水面上</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>稱質量</t>
+          <t>稱質量：天平是利用平衡原理測量物體質量的常用工具</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>排開水體積</t>
+          <t>排開水體積：把不規則物體放入水中，量出上升的水量，就等於物體排開的體積，這種方法叫排水法</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>特性</t>
+          <t>特性：密度是物質的特性之一，密度相同時可以初步懷疑是同一種物質，但仍需其他證據進一步確認</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>浮於水</t>
+          <t>浮於水：冰的密度比液態水小，所以冰塊會浮在水面上，這也是水結冰時體積會膨脹的緣故</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>40/5</t>
+          <t>40/5：密度=質量÷體積，40克除以5立方公分等於8g/cm³</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>D×V</t>
+          <t>D×V：質量=密度×體積，2g/cm³乘以10cm³等於20公克</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>特性不變</t>
+          <t>特性不變：密度是物質的特性，不論把物體切成多小塊，質量和體積會以相同比例減少，密度不會改變</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>小於水</t>
+          <t>小於水：這種油的密度0.8比水的密度1小，所以會浮在水面上</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>鋁密度</t>
+          <t>鋁密度：密度=質量÷體積，54克除以20立方公分等於2.7g/cm³，剛好符合鋁的密度</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>高密度液</t>
+          <t>高密度液：常見液體中，水銀的密度特別高，約為13.6g/cm³，遠高於水或油</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>16/2</t>
+          <t>16/2：密度=質量÷體積，16克除以2立方公分等於8g/cm³</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>100/50</t>
+          <t>100/50：密度=質量÷體積，100公克除以50立方公分等於2g/cm³</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>D×V</t>
+          <t>D×V：質量=密度×體積，4g/cm³乘以3立方公分等於12公克</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>同物質特性</t>
+          <t>同物質特性：不論是完整的鐵球還是細碎的鐵屑，只要都是純鐵，密度這個物質特性就相同，不會因形狀改變</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>整體考量</t>
+          <t>整體考量：船身做成中空的形狀，內部有大量空間，使得整艘船(含空氣)的平均密度小於水，所以能浮在水面上，這和鐵本身的密度大於水並不矛盾</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>約0.92</t>
+          <t>約0.92：能浮在水面上代表密度比水小，冰的密度約0.92g/cm³，比水的1g/cm³小，所以會浮起</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>分層</t>
+          <t>分層：兩種不互溶的液體混合後會依密度分層，密度較大的液體會沉到下層，密度較小的浮在上層</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>反比：密度=質量÷體積，質量不變時，體積變成兩倍，密度就會變成原來的一半，兩者成反比關係</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>60/20</t>
+          <t>60/20：排開的水體積等於物體體積，密度=質量÷體積，60公克除以20立方公分等於3g/cm³</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>比對特性值</t>
+          <t>比對特性值：純金的密度固定約為19.3g/cm³，鍍金的物品內部通常是其他金屬，整體密度會和純金不同，可以用測密度的方法來辨別真假</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>分子間距大</t>
+          <t>分子間距大：氣體分子之間的距離比固體、液體大很多，相同體積內含有的質量少很多，所以密度也小很多</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>密度</t>
+          <t>密度：鐵的密度比鋁大，相同體積下，密度越大代表單位體積內含的質量越多，所以鐵比較重</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>浮沉</t>
+          <t>浮沉：物體密度=質量÷體積=20÷25=0.8g/cm³，小於水的密度1g/cm³，密度比水小的物體會浮在水面上</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上1-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-4_三種難度測驗卷.xlsx
@@ -923,17 +923,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>下沉</t>
+          <t>D=M/V</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>天平</t>
+          <t>鐵,密度較大</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>鐵,密度較大</t>
+          <t>特性</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>小</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>減半</t>
+          <t>可初步判別</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>1 g/cm³</t>
+          <t>D=M/V</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1324,17 +1324,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>水銀</t>
+          <t>D=M/V</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>特性</t>
+          <t>排水法</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3 g/cm³</t>
+          <t>20 g</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>小</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>D=M/V</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>1 g/cm³</t>
+          <t>可初步判別</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>下層</t>
+          <t>水銀</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>下沉</t>
+          <t>可初步判別</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>減半</t>
+          <t>D=M/V</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>下沉</t>
+          <t>排水法</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>特性</t>
+          <t>減半</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>上浮</t>
+          <t>天平</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
